--- a/data/administracion_de_tribunales/OP_Ley148_ex_parteEmitidas.xlsx
+++ b/data/administracion_de_tribunales/OP_Ley148_ex_parteEmitidas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28813"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\administracion_de_tribunales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75E654C7-EE36-450F-AD65-6473A66E2AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BDEBED-C125-4321-93AF-42D103A1CCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-2021" sheetId="3" r:id="rId1"/>
@@ -106,7 +106,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,8 +159,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,16 +442,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="49" customWidth="1"/>
     <col min="4" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" customWidth="1"/>
+    <col min="6" max="6" width="42.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,7 +471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -485,7 +485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -496,7 +496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -536,7 +536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -553,7 +553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -573,7 +573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -593,7 +593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -610,7 +610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -630,7 +630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -640,7 +640,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -677,7 +677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -694,7 +694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -728,16 +728,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="49" customWidth="1"/>
     <col min="4" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" customWidth="1"/>
+    <col min="6" max="6" width="42.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -757,7 +757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -777,7 +777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -791,7 +791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -811,7 +811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -831,7 +831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -848,7 +848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -868,7 +868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -882,7 +882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -902,7 +902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -930,7 +930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -950,7 +950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -970,7 +970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -990,7 +990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1024,16 +1024,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="49" customWidth="1"/>
     <col min="4" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" customWidth="1"/>
+    <col min="6" max="6" width="42.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1308,16 +1308,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348633A4-A3DA-4647-A08B-2441CE4CA117}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="49" customWidth="1"/>
     <col min="4" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" customWidth="1"/>
+    <col min="6" max="6" width="42.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
@@ -1610,9 +1610,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2F5A0C-1199-45EA-85B9-B212D094D2B7}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1632,236 +1632,289 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
       </c>
       <c r="E2" s="3">
-        <v>4</v>
-      </c>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6">
+        <v>7</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="B3" s="3">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="C4" s="3">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7</v>
+      </c>
       <c r="E4" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3">
+        <v>53</v>
+      </c>
+      <c r="C5" s="3">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>3</v>
-      </c>
       <c r="E5" s="3">
-        <v>3</v>
-      </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E7" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6">
+        <v>4</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C12" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E12" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C13" s="3">
-        <v>2</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3">
+        <v>6</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="3">
-        <v>71</v>
+        <f>SUM(B2:B14)</f>
+        <v>264</v>
       </c>
       <c r="C15" s="3">
-        <v>25</v>
+        <f t="shared" ref="C15:F15" si="0">SUM(C2:C14)</f>
+        <v>109</v>
       </c>
       <c r="D15" s="3">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>70</v>
       </c>
       <c r="E15" s="3">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>95</v>
       </c>
       <c r="F15" s="3">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
